--- a/fundraiser_forms/011_public_awareness_campaign_donation_form--fundraiser_forms.xlsx
+++ b/fundraiser_forms/011_public_awareness_campaign_donation_form--fundraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>amount_one</t>
+          <t>amount one</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>amount_two</t>
+          <t>amount two</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>amount_three</t>
+          <t>amount three</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>amount_four</t>
+          <t>amount four</t>
         </is>
       </c>
     </row>
@@ -1296,102 +1296,102 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>donation_currency_choices</t>
+          <t>gift_card_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>usd</t>
+          <t>gift_card_yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>usd</t>
+          <t>gift card yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>donation_currency_choices</t>
+          <t>gift_card_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>chf</t>
+          <t>gift_card_no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>chf</t>
+          <t>gift card no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gift_card_choices</t>
+          <t>recurring_donation_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gift_card_yes</t>
+          <t>recurring_donation_no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gift_card_yes</t>
+          <t>recurring donation no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gift_card_choices</t>
+          <t>recurring_donation_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gift_card_no</t>
+          <t>recurring_donation_yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gift_card_no</t>
+          <t>recurring donation yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>recurring_donation_choices</t>
+          <t>donation_frequency_duration_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>recurring_donation_no</t>
+          <t>one_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>recurring_donation_no</t>
+          <t>one time</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>recurring_donation_choices</t>
+          <t>donation_frequency_duration_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>recurring_donation_yes</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>recurring_donation_yes</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>one_time</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>one_time</t>
+          <t>quarterly</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annually</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>bi_annually</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>bi annually</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>monthly_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>annually</t>
+          <t>monthly 3</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bi_annually</t>
+          <t>monthly_6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bi_annually</t>
+          <t>monthly 6</t>
         </is>
       </c>
     </row>
@@ -1488,46 +1488,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>monthly_3</t>
+          <t>monthly_12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>monthly_3</t>
+          <t>monthly 12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>donation_frequency_duration_choices</t>
+          <t>donation_currency_interval_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>monthly_6</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>monthly_6</t>
+          <t>usd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>donation_frequency_duration_choices</t>
+          <t>donation_currency_interval_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>monthly_12</t>
+          <t>cad</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>monthly_12</t>
+          <t>cad</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>usd</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>usd</t>
+          <t>eur</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>cad</t>
+          <t>gbp</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>cad</t>
+          <t>gbp</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>jpy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>eur</t>
+          <t>jpy</t>
         </is>
       </c>
     </row>
@@ -1590,80 +1590,80 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gbp</t>
+          <t>chf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gbp</t>
+          <t>chf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>donation_currency_interval_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jpy</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jpy</t>
+          <t>stripe</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>donation_currency_interval_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>chf</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>chf</t>
+          <t>paypal</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>donation_currency_interval_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>usd</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>usd</t>
+          <t>bank transfer</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>donation_currency_interval_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>chf</t>
+          <t>cash_app</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>chf</t>
+          <t>cash app</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>check</t>
         </is>
       </c>
     </row>
@@ -1692,163 +1692,95 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_status_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bank_transfer</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>bank_transfer</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_status_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>cash_app</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cash_app</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_status_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>check</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>check</t>
+          <t>cancelled</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>acknowledgement_sent_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>acknowledgement_sent_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>payment_status_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>payment_status_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>acknowledgement_sent_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>acknowledgement_sent_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
         <is>
           <t>No</t>
         </is>
